--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 68 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1734,8 +1734,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1835,8 +1835,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8663,8 +8663,8 @@
       <c r="P78" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" s="9" t="n">
-        <v>1</v>
+      <c r="Q78" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>1</v>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9813,8 +9813,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -14029,7 +14029,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14524,7 +14524,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14623,7 +14623,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1743,7 +1747,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1844,7 +1852,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2256,7 +2268,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2874,7 +2890,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3076,7 +3096,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4211,7 +4235,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4312,7 +4340,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4518,7 +4550,11 @@
       <c r="AB37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4720,7 +4756,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4821,7 +4861,11 @@
       <c r="AB40" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5225,7 +5269,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5326,7 +5374,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5528,7 +5580,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6554,7 +6610,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6861,7 +6921,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7677,7 +7741,11 @@
       <c r="AB68" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -9410,7 +9478,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9923,7 +9995,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10432,7 +10508,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -11563,7 +11643,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11769,7 +11853,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11971,7 +12059,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -13498,7 +13590,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13906,7 +14002,11 @@
       <c r="AB129" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC129"/>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2574,8 +2574,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="9" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4094,8 +4094,8 @@
       <c r="P33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="9" t="n">
-        <v>1</v>
+      <c r="Q33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="10" t="n">
         <v>1</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5979,8 +5979,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6084,8 +6084,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7302,8 +7302,8 @@
       <c r="S64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10165,8 +10165,8 @@
       <c r="P92" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" s="9" t="n">
-        <v>1</v>
+      <c r="Q92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12020,8 +12020,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P110" s="9" t="n">
-        <v>3</v>
+      <c r="P110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q110" s="10" t="n">
         <v>2</v>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="R125" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S125" s="10" t="n">
         <v>6</v>
@@ -13567,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="U125" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V125" s="9" t="n">
         <v>0</v>
@@ -13581,8 +13581,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13674,8 +13674,8 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>3</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14426,7 +14426,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14525,7 +14525,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14855,13 +14855,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1305,11 +1305,11 @@
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="S6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1948,8 +1948,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3503,8 +3503,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3814,8 +3814,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4436,8 +4436,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4541,8 +4541,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4735,11 +4735,11 @@
       <c r="U39" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>3</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5763,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" s="9" t="n">
         <v>3</v>
@@ -5777,8 +5777,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="10" t="n">
         <v>1</v>
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>5</v>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6500,8 +6500,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6706,8 +6706,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6811,8 +6811,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6912,8 +6912,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6997,10 +6997,10 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7421,8 +7421,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7522,8 +7522,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7600,14 +7600,14 @@
       <c r="P67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" s="9" t="n">
-        <v>1</v>
+      <c r="Q67" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="n">
         <v>1</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7717,8 +7717,8 @@
       <c r="T68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U68" s="9" t="n">
-        <v>0</v>
+      <c r="U68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V68" s="9" t="n">
         <v>1</v>
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7938,8 +7938,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="10" t="n">
         <v>1</v>
@@ -8144,8 +8144,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8245,8 +8245,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="9" t="n">
         <v>0</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8657,8 +8657,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8803,13 +8803,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8859,8 +8859,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9784,8 +9784,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9986,8 +9986,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10604,8 +10604,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10639,7 +10639,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10691,8 +10691,8 @@
       <c r="S97" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10814,8 +10814,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10915,8 +10915,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11117,8 +11117,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11166,13 +11166,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11222,8 +11222,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11634,8 +11634,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>3</v>
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12260,8 +12260,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12361,8 +12361,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12406,10 +12406,10 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J114" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="J114" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1</v>
@@ -12462,8 +12462,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12874,8 +12874,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13076,8 +13076,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13156,8 +13156,8 @@
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="9" t="n">
-        <v>1</v>
+      <c r="S121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T121" s="10" t="n">
         <v>1</v>
@@ -13177,8 +13177,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13278,8 +13278,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13379,8 +13379,8 @@
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13480,8 +13480,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13791,8 +13791,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -14129,7 +14129,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14162,7 +14162,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14261,7 +14261,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14360,13 +14360,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14426,7 +14426,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14525,7 +14525,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14558,13 +14558,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -14591,7 +14591,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14789,7 +14789,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14822,7 +14822,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -14888,7 +14888,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14921,7 +14921,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14954,7 +14954,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1476,17 +1476,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1787,17 +1787,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1892,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2098,17 +2098,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2203,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2457,8 +2457,8 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>3</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="10" t="n">
         <v>2</v>
@@ -2872,8 +2872,8 @@
       <c r="V21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W21" s="9" t="n">
-        <v>3</v>
+      <c r="W21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2930,17 +2930,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2974,8 +2974,8 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>3</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3241,17 +3241,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3285,8 +3285,8 @@
       <c r="U25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3297,8 +3297,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3346,17 +3346,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-29</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3552,13 +3552,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3859,13 +3859,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3903,8 +3903,8 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>3</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>2</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="9" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4065,13 +4065,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4109,8 +4109,8 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>1</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4275,17 +4275,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4308,13 +4308,13 @@
         <v>2</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T35" s="9" t="n">
-        <v>0</v>
+      <c r="T35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U35" s="9" t="n">
         <v>0</v>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4485,17 +4485,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>2</v>
@@ -4739,7 +4739,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4796,17 +4796,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4844,7 +4844,7 @@
         <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>5</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5103,13 +5103,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>4</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5414,13 +5414,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5923,17 +5923,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5971,7 +5971,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>4</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6028,13 +6028,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>3</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6066,8 +6066,8 @@
       <c r="S52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T52" s="9" t="n">
-        <v>0</v>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
@@ -6075,8 +6075,8 @@
       <c r="V52" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W52" s="9" t="n">
-        <v>0</v>
+      <c r="W52" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>4</v>
@@ -6133,17 +6133,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6238,13 +6238,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6339,17 +6339,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6589,11 +6589,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -6650,17 +6650,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6695,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6755,17 +6755,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6799,8 +6799,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>0</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6900,11 +6900,11 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>0</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>6</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7062,13 +7062,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7163,13 +7163,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7264,13 +7264,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7571,13 +7571,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>2</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8189,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8294,13 +8294,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8395,17 +8395,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8443,7 +8443,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>6</v>
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8645,11 +8645,11 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>0</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -8702,13 +8702,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8803,13 +8803,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8948,8 +8948,8 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>3</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9049,8 +9049,8 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>2</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9106,13 +9106,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9207,13 +9207,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9308,17 +9308,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9518,17 +9518,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9562,8 +9562,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>1</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9623,13 +9623,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9728,17 +9728,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9829,13 +9829,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9930,17 +9930,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9975,7 +9975,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10136,17 +10136,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10241,13 +10241,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10342,13 +10342,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10443,13 +10443,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10490,8 +10490,8 @@
       <c r="V95" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>3</v>
+      <c r="W95" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>6</v>
@@ -10548,17 +10548,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10593,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10653,17 +10653,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10689,7 +10689,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T97" s="10" t="n">
         <v>1</v>
@@ -10758,13 +10758,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10859,17 +10859,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10960,13 +10960,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11061,17 +11061,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11267,17 +11267,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11372,13 +11372,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11399,10 +11399,10 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
@@ -11410,11 +11410,11 @@
       <c r="S104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
         <v>4</v>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11578,17 +11578,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11683,13 +11683,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11788,13 +11788,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11893,13 +11893,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11994,17 +11994,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12099,13 +12099,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12204,13 +12204,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12305,13 +12305,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12406,13 +12406,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12507,17 +12507,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12543,7 +12543,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -12552,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12612,17 +12612,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12647,8 +12647,8 @@
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="9" t="n">
-        <v>1</v>
+      <c r="S116" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T116" s="10" t="n">
         <v>1</v>
@@ -12657,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12919,13 +12919,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -13020,13 +13020,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13121,13 +13121,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13323,17 +13323,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13364,8 +13364,8 @@
       <c r="T123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
+      <c r="U123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V123" s="10" t="n">
         <v>4</v>
@@ -13424,13 +13424,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13525,13 +13525,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13569,11 +13569,11 @@
       <c r="U125" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W125" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>4</v>
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -13735,13 +13735,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13836,13 +13836,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13937,17 +13937,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q129" s="10" t="n">
         <v>2</v>
@@ -13978,8 +13978,8 @@
       <c r="T129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
+      <c r="U129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V129" s="9" t="n">
         <v>2</v>
@@ -14144,7 +14144,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -14177,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -14195,7 +14195,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14210,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14228,7 +14228,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -14261,7 +14261,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -14294,7 +14294,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14342,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -14375,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -14426,7 +14426,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14441,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -14474,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14492,7 +14492,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -14606,7 +14606,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14624,7 +14624,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14657,7 +14657,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14690,7 +14690,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14705,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -14738,7 +14738,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14756,7 +14756,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14771,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -14804,7 +14804,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -14822,7 +14822,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14837,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -14870,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -14921,7 +14921,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14936,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -14954,7 +14954,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14969,7 +14969,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -14987,14 +14987,14 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1787,17 +1787,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="Q11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="T16" s="10" t="n">
         <v>1</v>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3174,8 +3174,8 @@
       <c r="S24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
+      <c r="T24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3793,8 +3793,8 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>1</v>
+      <c r="S30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T30" s="10" t="n">
         <v>1</v>
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="10" t="n">
         <v>1</v>
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4717,8 +4717,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
-        <v>3</v>
+      <c r="P39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>2</v>
@@ -4796,17 +4796,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -5414,13 +5414,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5559,8 +5559,8 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>3</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6028,13 +6028,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6057,8 +6057,8 @@
       <c r="P52" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" s="9" t="n">
-        <v>1</v>
+      <c r="Q52" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6180,8 +6180,8 @@
       <c r="V53" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W53" s="9" t="n">
-        <v>3</v>
+      <c r="W53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>5</v>
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -7163,13 +7163,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7781,13 +7781,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8189,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8233,8 +8233,8 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>3</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8395,13 +8395,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>6</v>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8544,8 +8544,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -9207,13 +9207,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10174,8 +10174,8 @@
       <c r="S92" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -10342,13 +10342,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11399,10 +11399,10 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q104" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q104" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11788,13 +11788,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11815,13 +11815,13 @@
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R108" s="9" t="n">
-        <v>1</v>
+      <c r="R108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11893,13 +11893,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>2</v>
       </c>
       <c r="R110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S110" s="9" t="n">
         <v>1</v>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13061,8 +13061,8 @@
       <c r="T120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
+      <c r="U120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V120" s="9" t="n">
         <v>3</v>
@@ -13323,13 +13323,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>6</v>
@@ -13424,13 +13424,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13735,13 +13735,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13836,13 +13836,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13937,13 +13937,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -14195,7 +14195,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14261,7 +14261,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14360,7 +14360,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -14375,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -14393,7 +14393,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -14426,13 +14426,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14591,7 +14591,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14822,13 +14822,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -14921,7 +14921,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/113/inyear.xlsx
+++ b/docs/d/113/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1712,16 +1712,16 @@
         <v>3</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1813,8 +1813,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P11" s="9" t="n">
-        <v>3</v>
+      <c r="P11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2334,8 +2334,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P16" s="9" t="n">
-        <v>3</v>
+      <c r="P16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2857,8 +2857,8 @@
       <c r="Q21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R21" s="9" t="n">
-        <v>1</v>
+      <c r="R21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S21" s="10" t="n">
         <v>2</v>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3276,8 +3276,8 @@
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="9" t="n">
-        <v>1</v>
+      <c r="S25" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T25" s="10" t="n">
         <v>1</v>
@@ -4101,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="9" t="n">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4529,11 +4529,11 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>2</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>4</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="10" t="n">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5544,8 +5544,8 @@
       <c r="P47" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q47" s="9" t="n">
-        <v>0</v>
+      <c r="Q47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5556,8 +5556,8 @@
       <c r="T47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
+      <c r="U47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V47" s="10" t="n">
         <v>4</v>
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5765,8 +5765,8 @@
       <c r="U49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>3</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5970,8 +5970,8 @@
       <c r="V51" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W51" s="9" t="n">
-        <v>2</v>
+      <c r="W51" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>4</v>
@@ -6028,13 +6028,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>4</v>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6383,8 +6383,8 @@
       <c r="U55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>2</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6755,17 +6755,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7062,13 +7062,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7510,8 +7510,8 @@
       <c r="U66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>3</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7571,13 +7571,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7615,8 +7615,8 @@
       <c r="U67" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Innovación Y Liderazgo</t>
+          <t>INNOVACION Y LIDERAZGO - CANACO CULIACAN</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -8601,17 +8601,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8649,7 +8649,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -8702,13 +8702,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9308,13 +9308,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9559,14 +9559,14 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10342,13 +10342,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10386,11 +10386,11 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>2</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" s="9" t="n">
         <v>2</v>
@@ -10443,13 +10443,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>6</v>
@@ -10859,13 +10859,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11398,8 +11398,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P104" s="9" t="n">
-        <v>3</v>
+      <c r="P104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q104" s="10" t="n">
         <v>2</v>
@@ -11994,13 +11994,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12134,8 +12134,8 @@
       <c r="R111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S111" s="9" t="n">
-        <v>1</v>
+      <c r="S111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T111" s="10" t="n">
         <v>1</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12542,8 +12542,8 @@
       <c r="R115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S115" s="9" t="n">
-        <v>1</v>
+      <c r="S115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -13323,13 +13323,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13424,13 +13424,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="R125" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S125" s="10" t="n">
         <v>6</v>
@@ -14129,7 +14129,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14162,7 +14162,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14228,7 +14228,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -14261,13 +14261,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14393,13 +14393,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14426,13 +14426,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -14558,13 +14558,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -14639,7 +14639,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -14690,7 +14690,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -14822,7 +14822,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -14855,7 +14855,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -14888,7 +14888,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
